--- a/exports/btc-usd_predictions_last90.xlsx
+++ b/exports/btc-usd_predictions_last90.xlsx
@@ -453,1441 +453,1441 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-08-16</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>117491.35</v>
+        <v>116252.31</v>
       </c>
       <c r="C2" t="n">
-        <v>116967.56</v>
+        <v>116717.6</v>
       </c>
       <c r="D2" t="n">
-        <v>-523.79</v>
+        <v>465.29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>117453.06</v>
+        <v>112831.18</v>
       </c>
       <c r="C3" t="n">
-        <v>117606.73</v>
+        <v>114973.14</v>
       </c>
       <c r="D3" t="n">
-        <v>153.67</v>
+        <v>2141.96</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>116252.31</v>
+        <v>114274.74</v>
       </c>
       <c r="C4" t="n">
-        <v>116726.6</v>
+        <v>114076.68</v>
       </c>
       <c r="D4" t="n">
-        <v>474.29</v>
+        <v>-198.06</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>112831.18</v>
+        <v>112419.03</v>
       </c>
       <c r="C5" t="n">
-        <v>114986.05</v>
+        <v>113826.14</v>
       </c>
       <c r="D5" t="n">
-        <v>2154.87</v>
+        <v>1407.11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>114274.74</v>
+        <v>116874.09</v>
       </c>
       <c r="C6" t="n">
-        <v>114093.02</v>
+        <v>114060</v>
       </c>
       <c r="D6" t="n">
-        <v>-181.73</v>
+        <v>-2814.09</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>112419.03</v>
+        <v>115374.33</v>
       </c>
       <c r="C7" t="n">
-        <v>113835.69</v>
+        <v>116096.52</v>
       </c>
       <c r="D7" t="n">
-        <v>1416.66</v>
+        <v>722.1900000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>116874.09</v>
+        <v>113458.43</v>
       </c>
       <c r="C8" t="n">
-        <v>114069.54</v>
+        <v>115053.01</v>
       </c>
       <c r="D8" t="n">
-        <v>-2804.55</v>
+        <v>1594.58</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>115374.33</v>
+        <v>110124.35</v>
       </c>
       <c r="C9" t="n">
-        <v>116097.52</v>
+        <v>112404.54</v>
       </c>
       <c r="D9" t="n">
-        <v>723.1900000000001</v>
+        <v>2280.19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>113458.43</v>
+        <v>111802.66</v>
       </c>
       <c r="C10" t="n">
-        <v>115058.5</v>
+        <v>110846.35</v>
       </c>
       <c r="D10" t="n">
-        <v>1600.07</v>
+        <v>-956.3099999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>110124.35</v>
+        <v>111222.06</v>
       </c>
       <c r="C11" t="n">
-        <v>112420</v>
+        <v>111491.11</v>
       </c>
       <c r="D11" t="n">
-        <v>2295.65</v>
+        <v>269.05</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>111802.66</v>
+        <v>112544.8</v>
       </c>
       <c r="C12" t="n">
-        <v>110866.47</v>
+        <v>111328.25</v>
       </c>
       <c r="D12" t="n">
-        <v>-936.1900000000001</v>
+        <v>-1216.55</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>111222.06</v>
+        <v>108410.84</v>
       </c>
       <c r="C13" t="n">
-        <v>111503.26</v>
+        <v>111075.77</v>
       </c>
       <c r="D13" t="n">
-        <v>281.19</v>
+        <v>2664.94</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>112544.8</v>
+        <v>108808.07</v>
       </c>
       <c r="C14" t="n">
-        <v>111336.79</v>
+        <v>109071.04</v>
       </c>
       <c r="D14" t="n">
-        <v>-1208.01</v>
+        <v>262.97</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>108410.84</v>
+        <v>108236.71</v>
       </c>
       <c r="C15" t="n">
-        <v>111083.16</v>
+        <v>108851.4</v>
       </c>
       <c r="D15" t="n">
-        <v>2672.32</v>
+        <v>614.6799999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>108808.07</v>
+        <v>109250.59</v>
       </c>
       <c r="C16" t="n">
-        <v>109086.51</v>
+        <v>108700.74</v>
       </c>
       <c r="D16" t="n">
-        <v>278.44</v>
+        <v>-549.86</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>108236.71</v>
+        <v>111200.59</v>
       </c>
       <c r="C17" t="n">
-        <v>108864.28</v>
+        <v>109818.84</v>
       </c>
       <c r="D17" t="n">
-        <v>627.5700000000001</v>
+        <v>-1381.74</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>109250.59</v>
+        <v>111723.21</v>
       </c>
       <c r="C18" t="n">
-        <v>108709.09</v>
+        <v>111329.38</v>
       </c>
       <c r="D18" t="n">
-        <v>-541.5</v>
+        <v>-393.84</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>111200.59</v>
+        <v>110723.6</v>
       </c>
       <c r="C19" t="n">
-        <v>109823.85</v>
+        <v>111620.19</v>
       </c>
       <c r="D19" t="n">
-        <v>-1376.74</v>
+        <v>896.59</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>111723.21</v>
+        <v>110650.98</v>
       </c>
       <c r="C20" t="n">
-        <v>111330.71</v>
+        <v>110589.75</v>
       </c>
       <c r="D20" t="n">
-        <v>-392.5</v>
+        <v>-61.23</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>110723.6</v>
+        <v>110224.7</v>
       </c>
       <c r="C21" t="n">
-        <v>111623.52</v>
+        <v>110381.04</v>
       </c>
       <c r="D21" t="n">
-        <v>899.92</v>
+        <v>156.35</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>110650.98</v>
+        <v>111167.62</v>
       </c>
       <c r="C22" t="n">
-        <v>110598.13</v>
+        <v>110236.02</v>
       </c>
       <c r="D22" t="n">
-        <v>-52.85</v>
+        <v>-931.6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>110224.7</v>
+        <v>112071.43</v>
       </c>
       <c r="C23" t="n">
-        <v>110392.09</v>
+        <v>111028.33</v>
       </c>
       <c r="D23" t="n">
-        <v>167.4</v>
+        <v>-1043.1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>111167.62</v>
+        <v>111530.55</v>
       </c>
       <c r="C24" t="n">
-        <v>110246.65</v>
+        <v>111671.94</v>
       </c>
       <c r="D24" t="n">
-        <v>-920.97</v>
+        <v>141.39</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>112071.43</v>
+        <v>113955.36</v>
       </c>
       <c r="C25" t="n">
-        <v>111035.52</v>
+        <v>112220.32</v>
       </c>
       <c r="D25" t="n">
-        <v>-1035.91</v>
+        <v>-1735.04</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>111530.55</v>
+        <v>115507.54</v>
       </c>
       <c r="C26" t="n">
-        <v>111677.31</v>
+        <v>114155.04</v>
       </c>
       <c r="D26" t="n">
-        <v>146.76</v>
+        <v>-1352.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>113955.36</v>
+        <v>116101.58</v>
       </c>
       <c r="C27" t="n">
-        <v>112228.04</v>
+        <v>115340.89</v>
       </c>
       <c r="D27" t="n">
-        <v>-1727.32</v>
+        <v>-760.6900000000001</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>115507.54</v>
+        <v>115950.51</v>
       </c>
       <c r="C28" t="n">
-        <v>114158.44</v>
+        <v>115343.02</v>
       </c>
       <c r="D28" t="n">
-        <v>-1349.09</v>
+        <v>-607.48</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>116101.58</v>
+        <v>115407.66</v>
       </c>
       <c r="C29" t="n">
-        <v>115343.07</v>
+        <v>115363.79</v>
       </c>
       <c r="D29" t="n">
-        <v>-758.51</v>
+        <v>-43.86</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>115950.51</v>
+        <v>115444.88</v>
       </c>
       <c r="C30" t="n">
-        <v>115350.29</v>
+        <v>115145.13</v>
       </c>
       <c r="D30" t="n">
-        <v>-600.22</v>
+        <v>-299.75</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>115407.66</v>
+        <v>116843.19</v>
       </c>
       <c r="C31" t="n">
-        <v>115373.33</v>
+        <v>115371.04</v>
       </c>
       <c r="D31" t="n">
-        <v>-34.33</v>
+        <v>-1472.14</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>115444.88</v>
+        <v>116468.51</v>
       </c>
       <c r="C32" t="n">
-        <v>115155.89</v>
+        <v>116267.87</v>
       </c>
       <c r="D32" t="n">
-        <v>-288.98</v>
+        <v>-200.64</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>116843.19</v>
+        <v>117137.2</v>
       </c>
       <c r="C33" t="n">
-        <v>115381.3</v>
+        <v>116453.95</v>
       </c>
       <c r="D33" t="n">
-        <v>-1461.88</v>
+        <v>-683.25</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>116468.51</v>
+        <v>115688.86</v>
       </c>
       <c r="C34" t="n">
-        <v>116273.98</v>
+        <v>116549.89</v>
       </c>
       <c r="D34" t="n">
-        <v>-194.53</v>
+        <v>861.03</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>117137.2</v>
+        <v>115721.96</v>
       </c>
       <c r="C35" t="n">
-        <v>116460.71</v>
+        <v>115749.88</v>
       </c>
       <c r="D35" t="n">
-        <v>-676.5</v>
+        <v>27.92</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>115688.86</v>
+        <v>115306.09</v>
       </c>
       <c r="C36" t="n">
-        <v>116556.04</v>
+        <v>115447.29</v>
       </c>
       <c r="D36" t="n">
-        <v>867.1799999999999</v>
+        <v>141.2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>115721.96</v>
+        <v>112748.51</v>
       </c>
       <c r="C37" t="n">
-        <v>115759.91</v>
+        <v>114273.47</v>
       </c>
       <c r="D37" t="n">
-        <v>37.95</v>
+        <v>1524.96</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>115306.09</v>
+        <v>112014.5</v>
       </c>
       <c r="C38" t="n">
-        <v>115456.6</v>
+        <v>112470.58</v>
       </c>
       <c r="D38" t="n">
-        <v>150.51</v>
+        <v>456.08</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>112748.51</v>
+        <v>113328.63</v>
       </c>
       <c r="C39" t="n">
-        <v>114283.18</v>
+        <v>112517.45</v>
       </c>
       <c r="D39" t="n">
-        <v>1534.67</v>
+        <v>-811.1799999999999</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>112014.5</v>
+        <v>109049.29</v>
       </c>
       <c r="C40" t="n">
-        <v>112486.02</v>
+        <v>112108.59</v>
       </c>
       <c r="D40" t="n">
-        <v>471.52</v>
+        <v>3059.3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>113328.63</v>
+        <v>109712.83</v>
       </c>
       <c r="C41" t="n">
-        <v>112530</v>
+        <v>109468.21</v>
       </c>
       <c r="D41" t="n">
-        <v>-798.63</v>
+        <v>-244.62</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>109049.29</v>
+        <v>109681.95</v>
       </c>
       <c r="C42" t="n">
-        <v>112114.42</v>
+        <v>109850.28</v>
       </c>
       <c r="D42" t="n">
-        <v>3065.14</v>
+        <v>168.34</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>109712.83</v>
+        <v>112122.64</v>
       </c>
       <c r="C43" t="n">
-        <v>109483.06</v>
+        <v>111056.8</v>
       </c>
       <c r="D43" t="n">
-        <v>-229.77</v>
+        <v>-1065.84</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>109681.95</v>
+        <v>114400.38</v>
       </c>
       <c r="C44" t="n">
-        <v>109861.96</v>
+        <v>112811.3</v>
       </c>
       <c r="D44" t="n">
-        <v>180.02</v>
+        <v>-1589.08</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>112122.64</v>
+        <v>114056.09</v>
       </c>
       <c r="C45" t="n">
-        <v>111062.28</v>
+        <v>114214.56</v>
       </c>
       <c r="D45" t="n">
-        <v>-1060.36</v>
+        <v>158.47</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>114400.38</v>
+        <v>118648.93</v>
       </c>
       <c r="C46" t="n">
-        <v>112809.57</v>
+        <v>115810.44</v>
       </c>
       <c r="D46" t="n">
-        <v>-1590.81</v>
+        <v>-2838.49</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>114056.09</v>
+        <v>120681.26</v>
       </c>
       <c r="C47" t="n">
-        <v>114211.88</v>
+        <v>118835.61</v>
       </c>
       <c r="D47" t="n">
-        <v>155.79</v>
+        <v>-1845.65</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>118648.93</v>
+        <v>122266.53</v>
       </c>
       <c r="C48" t="n">
-        <v>115811.35</v>
+        <v>120679.4</v>
       </c>
       <c r="D48" t="n">
-        <v>-2837.58</v>
+        <v>-1587.13</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>120681.26</v>
+        <v>122425.43</v>
       </c>
       <c r="C49" t="n">
-        <v>118830.35</v>
+        <v>121343.35</v>
       </c>
       <c r="D49" t="n">
-        <v>-1850.9</v>
+        <v>-1082.08</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>122266.53</v>
+        <v>123513.48</v>
       </c>
       <c r="C50" t="n">
-        <v>120675.03</v>
+        <v>122238.08</v>
       </c>
       <c r="D50" t="n">
-        <v>-1591.5</v>
+        <v>-1275.4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>122425.43</v>
+        <v>124752.53</v>
       </c>
       <c r="C51" t="n">
-        <v>121344.69</v>
+        <v>123425.03</v>
       </c>
       <c r="D51" t="n">
-        <v>-1080.74</v>
+        <v>-1327.5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>123513.48</v>
+        <v>121451.38</v>
       </c>
       <c r="C52" t="n">
-        <v>122242.57</v>
+        <v>122981.88</v>
       </c>
       <c r="D52" t="n">
-        <v>-1270.9</v>
+        <v>1530.5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>124752.53</v>
+        <v>123354.87</v>
       </c>
       <c r="C53" t="n">
-        <v>123429.65</v>
+        <v>121738</v>
       </c>
       <c r="D53" t="n">
-        <v>-1322.88</v>
+        <v>-1616.86</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>121451.38</v>
+        <v>121705.59</v>
       </c>
       <c r="C54" t="n">
-        <v>122986.74</v>
+        <v>122569.1</v>
       </c>
       <c r="D54" t="n">
-        <v>1535.36</v>
+        <v>863.51</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>123354.87</v>
+        <v>113214.37</v>
       </c>
       <c r="C55" t="n">
-        <v>121751.64</v>
+        <v>119055.9</v>
       </c>
       <c r="D55" t="n">
-        <v>-1603.22</v>
+        <v>5841.53</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>121705.59</v>
+        <v>110807.88</v>
       </c>
       <c r="C56" t="n">
-        <v>122577.19</v>
+        <v>112359.59</v>
       </c>
       <c r="D56" t="n">
-        <v>871.6</v>
+        <v>1551.71</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>113214.37</v>
+        <v>115169.77</v>
       </c>
       <c r="C57" t="n">
-        <v>119066.98</v>
+        <v>112704.22</v>
       </c>
       <c r="D57" t="n">
-        <v>5852.61</v>
+        <v>-2465.55</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>110807.88</v>
+        <v>115271.08</v>
       </c>
       <c r="C58" t="n">
-        <v>112391.95</v>
+        <v>115833.15</v>
       </c>
       <c r="D58" t="n">
-        <v>1584.07</v>
+        <v>562.0700000000001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>115169.77</v>
+        <v>113118.66</v>
       </c>
       <c r="C59" t="n">
-        <v>112730.09</v>
+        <v>114555.47</v>
       </c>
       <c r="D59" t="n">
-        <v>-2439.67</v>
+        <v>1436.8</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>115271.08</v>
+        <v>110783.16</v>
       </c>
       <c r="C60" t="n">
-        <v>115834.38</v>
+        <v>112874.19</v>
       </c>
       <c r="D60" t="n">
-        <v>563.3</v>
+        <v>2091.02</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>113118.66</v>
+        <v>108186.04</v>
       </c>
       <c r="C61" t="n">
-        <v>114555.42</v>
+        <v>111223.64</v>
       </c>
       <c r="D61" t="n">
-        <v>1436.75</v>
+        <v>3037.6</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>110783.16</v>
+        <v>106467.79</v>
       </c>
       <c r="C62" t="n">
-        <v>112884.73</v>
+        <v>107918.51</v>
       </c>
       <c r="D62" t="n">
-        <v>2101.56</v>
+        <v>1450.72</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>108186.04</v>
+        <v>107198.27</v>
       </c>
       <c r="C63" t="n">
-        <v>111238.31</v>
+        <v>106397.3</v>
       </c>
       <c r="D63" t="n">
-        <v>3052.27</v>
+        <v>-800.97</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>106467.79</v>
+        <v>108666.71</v>
       </c>
       <c r="C64" t="n">
-        <v>107936.24</v>
+        <v>107851.52</v>
       </c>
       <c r="D64" t="n">
-        <v>1468.45</v>
+        <v>-815.2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>107198.27</v>
+        <v>110588.93</v>
       </c>
       <c r="C65" t="n">
-        <v>106415.22</v>
+        <v>109723.63</v>
       </c>
       <c r="D65" t="n">
-        <v>-783.05</v>
+        <v>-865.3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>108666.71</v>
+        <v>108476.89</v>
       </c>
       <c r="C66" t="n">
-        <v>107860.32</v>
+        <v>110112.24</v>
       </c>
       <c r="D66" t="n">
-        <v>-806.39</v>
+        <v>1635.35</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>110588.93</v>
+        <v>107688.59</v>
       </c>
       <c r="C67" t="n">
-        <v>109724.35</v>
+        <v>108549.15</v>
       </c>
       <c r="D67" t="n">
-        <v>-864.58</v>
+        <v>860.5599999999999</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>108476.89</v>
+        <v>110069.73</v>
       </c>
       <c r="C68" t="n">
-        <v>110111.64</v>
+        <v>108685.72</v>
       </c>
       <c r="D68" t="n">
-        <v>1634.75</v>
+        <v>-1384.01</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>107688.59</v>
+        <v>111033.92</v>
       </c>
       <c r="C69" t="n">
-        <v>108557.97</v>
+        <v>110265.73</v>
       </c>
       <c r="D69" t="n">
-        <v>869.38</v>
+        <v>-768.1900000000001</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-25</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>110069.73</v>
+        <v>111641.73</v>
       </c>
       <c r="C70" t="n">
-        <v>108696.57</v>
+        <v>110803.23</v>
       </c>
       <c r="D70" t="n">
-        <v>-1373.16</v>
+        <v>-838.5</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>111033.92</v>
+        <v>114472.45</v>
       </c>
       <c r="C71" t="n">
-        <v>110269.15</v>
+        <v>112317.65</v>
       </c>
       <c r="D71" t="n">
-        <v>-764.77</v>
+        <v>-2154.8</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2025-10-25</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>111641.73</v>
+        <v>114119.33</v>
       </c>
       <c r="C72" t="n">
-        <v>110806.24</v>
+        <v>114458.86</v>
       </c>
       <c r="D72" t="n">
-        <v>-835.49</v>
+        <v>339.54</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>114472.45</v>
+        <v>112956.16</v>
       </c>
       <c r="C73" t="n">
-        <v>112319.45</v>
+        <v>113663.47</v>
       </c>
       <c r="D73" t="n">
-        <v>-2152.99</v>
+        <v>707.3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>114119.33</v>
+        <v>110055.3</v>
       </c>
       <c r="C74" t="n">
-        <v>114457.04</v>
+        <v>111493.3</v>
       </c>
       <c r="D74" t="n">
-        <v>337.71</v>
+        <v>1437.99</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>112956.16</v>
+        <v>108305.55</v>
       </c>
       <c r="C75" t="n">
-        <v>113666.55</v>
+        <v>109337.25</v>
       </c>
       <c r="D75" t="n">
-        <v>710.38</v>
+        <v>1031.7</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>110055.3</v>
+        <v>109556.16</v>
       </c>
       <c r="C76" t="n">
-        <v>111505.99</v>
+        <v>108639.78</v>
       </c>
       <c r="D76" t="n">
-        <v>1450.69</v>
+        <v>-916.38</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>108305.55</v>
+        <v>110064.02</v>
       </c>
       <c r="C77" t="n">
-        <v>109356.37</v>
+        <v>109393.62</v>
       </c>
       <c r="D77" t="n">
-        <v>1050.83</v>
+        <v>-670.4</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>109556.16</v>
+        <v>110639.62</v>
       </c>
       <c r="C78" t="n">
-        <v>108657.19</v>
+        <v>110197.91</v>
       </c>
       <c r="D78" t="n">
-        <v>-898.97</v>
+        <v>-441.71</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>110064.02</v>
+        <v>106547.52</v>
       </c>
       <c r="C79" t="n">
-        <v>109404.09</v>
+        <v>109179.94</v>
       </c>
       <c r="D79" t="n">
-        <v>-659.92</v>
+        <v>2632.42</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>110639.62</v>
+        <v>101590.52</v>
       </c>
       <c r="C80" t="n">
-        <v>110203.92</v>
+        <v>104995.49</v>
       </c>
       <c r="D80" t="n">
-        <v>-435.7</v>
+        <v>3404.96</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>106547.52</v>
+        <v>103891.84</v>
       </c>
       <c r="C81" t="n">
-        <v>109187.45</v>
+        <v>102560.24</v>
       </c>
       <c r="D81" t="n">
-        <v>2639.93</v>
+        <v>-1331.6</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>101590.52</v>
+        <v>101301.29</v>
       </c>
       <c r="C82" t="n">
-        <v>105015.73</v>
+        <v>102591.89</v>
       </c>
       <c r="D82" t="n">
-        <v>3425.21</v>
+        <v>1290.6</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>103891.84</v>
+        <v>103372.41</v>
       </c>
       <c r="C83" t="n">
-        <v>102588.28</v>
+        <v>101987.12</v>
       </c>
       <c r="D83" t="n">
-        <v>-1303.56</v>
+        <v>-1385.28</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>101301.29</v>
+        <v>102282.12</v>
       </c>
       <c r="C84" t="n">
-        <v>102608.71</v>
+        <v>102598.25</v>
       </c>
       <c r="D84" t="n">
-        <v>1307.42</v>
+        <v>316.14</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>103372.41</v>
+        <v>104719.64</v>
       </c>
       <c r="C85" t="n">
-        <v>102000.86</v>
+        <v>103829.4</v>
       </c>
       <c r="D85" t="n">
-        <v>-1371.55</v>
+        <v>-890.25</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>102282.12</v>
+        <v>105996.59</v>
       </c>
       <c r="C86" t="n">
-        <v>102608.43</v>
+        <v>105362.05</v>
       </c>
       <c r="D86" t="n">
-        <v>326.31</v>
+        <v>-634.55</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>104719.64</v>
+        <v>102997.47</v>
       </c>
       <c r="C87" t="n">
-        <v>103837.8</v>
+        <v>104690.55</v>
       </c>
       <c r="D87" t="n">
-        <v>-881.84</v>
+        <v>1693.08</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>105996.59</v>
+        <v>101663.19</v>
       </c>
       <c r="C88" t="n">
-        <v>105363.98</v>
+        <v>102365.3</v>
       </c>
       <c r="D88" t="n">
-        <v>-632.62</v>
+        <v>702.11</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>102997.47</v>
+        <v>99697.49000000001</v>
       </c>
       <c r="C89" t="n">
-        <v>104693.7</v>
+        <v>100581.55</v>
       </c>
       <c r="D89" t="n">
-        <v>1696.23</v>
+        <v>884.05</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>101663.19</v>
+        <v>94397.78999999999</v>
       </c>
       <c r="C90" t="n">
-        <v>102381.17</v>
+        <v>97513.74000000001</v>
       </c>
       <c r="D90" t="n">
-        <v>717.98</v>
+        <v>3115.95</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>99697.49000000001</v>
+        <v>95549.14999999999</v>
       </c>
       <c r="C91" t="n">
-        <v>100600.16</v>
+        <v>94557.39</v>
       </c>
       <c r="D91" t="n">
-        <v>902.67</v>
+        <v>-991.76</v>
       </c>
     </row>
   </sheetData>

--- a/exports/btc-usd_predictions_last90.xlsx
+++ b/exports/btc-usd_predictions_last90.xlsx
@@ -453,1441 +453,1441 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>116252.31</v>
+        <v>116874.09</v>
       </c>
       <c r="C2" t="n">
-        <v>116717.6</v>
+        <v>114018.56</v>
       </c>
       <c r="D2" t="n">
-        <v>465.29</v>
+        <v>-2855.52</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>112831.18</v>
+        <v>115374.33</v>
       </c>
       <c r="C3" t="n">
-        <v>114973.14</v>
+        <v>116015.67</v>
       </c>
       <c r="D3" t="n">
-        <v>2141.96</v>
+        <v>641.34</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>114274.74</v>
+        <v>113458.43</v>
       </c>
       <c r="C4" t="n">
-        <v>114076.68</v>
+        <v>115040.63</v>
       </c>
       <c r="D4" t="n">
-        <v>-198.06</v>
+        <v>1582.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>112419.03</v>
+        <v>110124.35</v>
       </c>
       <c r="C5" t="n">
-        <v>113826.14</v>
+        <v>112355.35</v>
       </c>
       <c r="D5" t="n">
-        <v>1407.11</v>
+        <v>2231</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>116874.09</v>
+        <v>111802.66</v>
       </c>
       <c r="C6" t="n">
-        <v>114060</v>
+        <v>110806.5</v>
       </c>
       <c r="D6" t="n">
-        <v>-2814.09</v>
+        <v>-996.16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>115374.33</v>
+        <v>111222.06</v>
       </c>
       <c r="C7" t="n">
-        <v>116096.52</v>
+        <v>111414.71</v>
       </c>
       <c r="D7" t="n">
-        <v>722.1900000000001</v>
+        <v>192.65</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>113458.43</v>
+        <v>112544.8</v>
       </c>
       <c r="C8" t="n">
-        <v>115053.01</v>
+        <v>111297.07</v>
       </c>
       <c r="D8" t="n">
-        <v>1594.58</v>
+        <v>-1247.74</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>110124.35</v>
+        <v>108410.84</v>
       </c>
       <c r="C9" t="n">
-        <v>112404.54</v>
+        <v>111002.02</v>
       </c>
       <c r="D9" t="n">
-        <v>2280.19</v>
+        <v>2591.18</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>111802.66</v>
+        <v>108808.07</v>
       </c>
       <c r="C10" t="n">
-        <v>110846.35</v>
+        <v>109038.09</v>
       </c>
       <c r="D10" t="n">
-        <v>-956.3099999999999</v>
+        <v>230.02</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>111222.06</v>
+        <v>108236.71</v>
       </c>
       <c r="C11" t="n">
-        <v>111491.11</v>
+        <v>108772.81</v>
       </c>
       <c r="D11" t="n">
-        <v>269.05</v>
+        <v>536.1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>112544.8</v>
+        <v>109250.59</v>
       </c>
       <c r="C12" t="n">
-        <v>111328.25</v>
+        <v>108667.43</v>
       </c>
       <c r="D12" t="n">
-        <v>-1216.55</v>
+        <v>-583.16</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>108410.84</v>
+        <v>111200.59</v>
       </c>
       <c r="C13" t="n">
-        <v>111075.77</v>
+        <v>109760.84</v>
       </c>
       <c r="D13" t="n">
-        <v>2664.94</v>
+        <v>-1439.75</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>108808.07</v>
+        <v>111723.21</v>
       </c>
       <c r="C14" t="n">
-        <v>109071.04</v>
+        <v>111285.79</v>
       </c>
       <c r="D14" t="n">
-        <v>262.97</v>
+        <v>-437.42</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>108236.71</v>
+        <v>110723.6</v>
       </c>
       <c r="C15" t="n">
-        <v>108851.4</v>
+        <v>111589.03</v>
       </c>
       <c r="D15" t="n">
-        <v>614.6799999999999</v>
+        <v>865.4299999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>109250.59</v>
+        <v>110650.98</v>
       </c>
       <c r="C16" t="n">
-        <v>108700.74</v>
+        <v>110572.61</v>
       </c>
       <c r="D16" t="n">
-        <v>-549.86</v>
+        <v>-78.37</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>111200.59</v>
+        <v>110224.7</v>
       </c>
       <c r="C17" t="n">
-        <v>109818.84</v>
+        <v>110346.66</v>
       </c>
       <c r="D17" t="n">
-        <v>-1381.74</v>
+        <v>121.97</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>111723.21</v>
+        <v>111167.62</v>
       </c>
       <c r="C18" t="n">
-        <v>111329.38</v>
+        <v>110210.01</v>
       </c>
       <c r="D18" t="n">
-        <v>-393.84</v>
+        <v>-957.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>110723.6</v>
+        <v>112071.43</v>
       </c>
       <c r="C19" t="n">
-        <v>111620.19</v>
+        <v>110988.82</v>
       </c>
       <c r="D19" t="n">
-        <v>896.59</v>
+        <v>-1082.61</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>110650.98</v>
+        <v>111530.55</v>
       </c>
       <c r="C20" t="n">
-        <v>110589.75</v>
+        <v>111630.29</v>
       </c>
       <c r="D20" t="n">
-        <v>-61.23</v>
+        <v>99.75</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>110224.7</v>
+        <v>113955.36</v>
       </c>
       <c r="C21" t="n">
-        <v>110381.04</v>
+        <v>112184.35</v>
       </c>
       <c r="D21" t="n">
-        <v>156.35</v>
+        <v>-1771.01</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>111167.62</v>
+        <v>115507.54</v>
       </c>
       <c r="C22" t="n">
-        <v>110236.02</v>
+        <v>114106.48</v>
       </c>
       <c r="D22" t="n">
-        <v>-931.6</v>
+        <v>-1401.05</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>112071.43</v>
+        <v>116101.58</v>
       </c>
       <c r="C23" t="n">
-        <v>111028.33</v>
+        <v>115315.55</v>
       </c>
       <c r="D23" t="n">
-        <v>-1043.1</v>
+        <v>-786.03</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>111530.55</v>
+        <v>115950.51</v>
       </c>
       <c r="C24" t="n">
-        <v>111671.94</v>
+        <v>115335.68</v>
       </c>
       <c r="D24" t="n">
-        <v>141.39</v>
+        <v>-614.83</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>113955.36</v>
+        <v>115407.66</v>
       </c>
       <c r="C25" t="n">
-        <v>112220.32</v>
+        <v>115352.46</v>
       </c>
       <c r="D25" t="n">
-        <v>-1735.04</v>
+        <v>-55.19</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>115507.54</v>
+        <v>115444.88</v>
       </c>
       <c r="C26" t="n">
-        <v>114155.04</v>
+        <v>115123.87</v>
       </c>
       <c r="D26" t="n">
-        <v>-1352.5</v>
+        <v>-321</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>116101.58</v>
+        <v>116843.19</v>
       </c>
       <c r="C27" t="n">
-        <v>115340.89</v>
+        <v>115348.47</v>
       </c>
       <c r="D27" t="n">
-        <v>-760.6900000000001</v>
+        <v>-1494.72</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>115950.51</v>
+        <v>116468.51</v>
       </c>
       <c r="C28" t="n">
-        <v>115343.02</v>
+        <v>116236.09</v>
       </c>
       <c r="D28" t="n">
-        <v>-607.48</v>
+        <v>-232.42</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>115407.66</v>
+        <v>117137.2</v>
       </c>
       <c r="C29" t="n">
-        <v>115363.79</v>
+        <v>116439.63</v>
       </c>
       <c r="D29" t="n">
-        <v>-43.86</v>
+        <v>-697.58</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>115444.88</v>
+        <v>115688.86</v>
       </c>
       <c r="C30" t="n">
-        <v>115145.13</v>
+        <v>116514.53</v>
       </c>
       <c r="D30" t="n">
-        <v>-299.75</v>
+        <v>825.67</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>116843.19</v>
+        <v>115721.96</v>
       </c>
       <c r="C31" t="n">
-        <v>115371.04</v>
+        <v>115734.45</v>
       </c>
       <c r="D31" t="n">
-        <v>-1472.14</v>
+        <v>12.48</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>116468.51</v>
+        <v>115306.09</v>
       </c>
       <c r="C32" t="n">
-        <v>116267.87</v>
+        <v>115400.58</v>
       </c>
       <c r="D32" t="n">
-        <v>-200.64</v>
+        <v>94.48999999999999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>117137.2</v>
+        <v>112748.51</v>
       </c>
       <c r="C33" t="n">
-        <v>116453.95</v>
+        <v>114235.36</v>
       </c>
       <c r="D33" t="n">
-        <v>-683.25</v>
+        <v>1486.85</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>115688.86</v>
+        <v>112014.5</v>
       </c>
       <c r="C34" t="n">
-        <v>116549.89</v>
+        <v>112434.18</v>
       </c>
       <c r="D34" t="n">
-        <v>861.03</v>
+        <v>419.68</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>115721.96</v>
+        <v>113328.63</v>
       </c>
       <c r="C35" t="n">
-        <v>115749.88</v>
+        <v>112460.82</v>
       </c>
       <c r="D35" t="n">
-        <v>27.92</v>
+        <v>-867.8099999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>115306.09</v>
+        <v>109049.29</v>
       </c>
       <c r="C36" t="n">
-        <v>115447.29</v>
+        <v>112045.83</v>
       </c>
       <c r="D36" t="n">
-        <v>141.2</v>
+        <v>2996.54</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>112748.51</v>
+        <v>109712.83</v>
       </c>
       <c r="C37" t="n">
-        <v>114273.47</v>
+        <v>109441.45</v>
       </c>
       <c r="D37" t="n">
-        <v>1524.96</v>
+        <v>-271.38</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>112014.5</v>
+        <v>109681.95</v>
       </c>
       <c r="C38" t="n">
-        <v>112470.58</v>
+        <v>109761.02</v>
       </c>
       <c r="D38" t="n">
-        <v>456.08</v>
+        <v>79.06999999999999</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>113328.63</v>
+        <v>112122.64</v>
       </c>
       <c r="C39" t="n">
-        <v>112517.45</v>
+        <v>111010.85</v>
       </c>
       <c r="D39" t="n">
-        <v>-811.1799999999999</v>
+        <v>-1111.79</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>109049.29</v>
+        <v>114400.38</v>
       </c>
       <c r="C40" t="n">
-        <v>112108.59</v>
+        <v>112761.19</v>
       </c>
       <c r="D40" t="n">
-        <v>3059.3</v>
+        <v>-1639.2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>109712.83</v>
+        <v>114056.09</v>
       </c>
       <c r="C41" t="n">
-        <v>109468.21</v>
+        <v>114198.43</v>
       </c>
       <c r="D41" t="n">
-        <v>-244.62</v>
+        <v>142.34</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>109681.95</v>
+        <v>118648.93</v>
       </c>
       <c r="C42" t="n">
-        <v>109850.28</v>
+        <v>115801.38</v>
       </c>
       <c r="D42" t="n">
-        <v>168.34</v>
+        <v>-2847.55</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>112122.64</v>
+        <v>120681.26</v>
       </c>
       <c r="C43" t="n">
-        <v>111056.8</v>
+        <v>118819.74</v>
       </c>
       <c r="D43" t="n">
-        <v>-1065.84</v>
+        <v>-1861.51</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>114400.38</v>
+        <v>122266.53</v>
       </c>
       <c r="C44" t="n">
-        <v>112811.3</v>
+        <v>120716.81</v>
       </c>
       <c r="D44" t="n">
-        <v>-1589.08</v>
+        <v>-1549.72</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>114056.09</v>
+        <v>122425.43</v>
       </c>
       <c r="C45" t="n">
-        <v>114214.56</v>
+        <v>121380.3</v>
       </c>
       <c r="D45" t="n">
-        <v>158.47</v>
+        <v>-1045.12</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>118648.93</v>
+        <v>123513.48</v>
       </c>
       <c r="C46" t="n">
-        <v>115810.44</v>
+        <v>122271.32</v>
       </c>
       <c r="D46" t="n">
-        <v>-2838.49</v>
+        <v>-1242.15</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>120681.26</v>
+        <v>124752.53</v>
       </c>
       <c r="C47" t="n">
-        <v>118835.61</v>
+        <v>123443.39</v>
       </c>
       <c r="D47" t="n">
-        <v>-1845.65</v>
+        <v>-1309.14</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>122266.53</v>
+        <v>121451.38</v>
       </c>
       <c r="C48" t="n">
-        <v>120679.4</v>
+        <v>123009.88</v>
       </c>
       <c r="D48" t="n">
-        <v>-1587.13</v>
+        <v>1558.49</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>122425.43</v>
+        <v>123354.87</v>
       </c>
       <c r="C49" t="n">
-        <v>121343.35</v>
+        <v>121759.14</v>
       </c>
       <c r="D49" t="n">
-        <v>-1082.08</v>
+        <v>-1595.73</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>123513.48</v>
+        <v>121705.59</v>
       </c>
       <c r="C50" t="n">
-        <v>122238.08</v>
+        <v>122529.17</v>
       </c>
       <c r="D50" t="n">
-        <v>-1275.4</v>
+        <v>823.58</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>124752.53</v>
+        <v>113214.37</v>
       </c>
       <c r="C51" t="n">
-        <v>123425.03</v>
+        <v>119047.49</v>
       </c>
       <c r="D51" t="n">
-        <v>-1327.5</v>
+        <v>5833.12</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>121451.38</v>
+        <v>110807.88</v>
       </c>
       <c r="C52" t="n">
-        <v>122981.88</v>
+        <v>112331.47</v>
       </c>
       <c r="D52" t="n">
-        <v>1530.5</v>
+        <v>1523.59</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>123354.87</v>
+        <v>115169.77</v>
       </c>
       <c r="C53" t="n">
-        <v>121738</v>
+        <v>112581.73</v>
       </c>
       <c r="D53" t="n">
-        <v>-1616.86</v>
+        <v>-2588.03</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>121705.59</v>
+        <v>115271.08</v>
       </c>
       <c r="C54" t="n">
-        <v>122569.1</v>
+        <v>115717.93</v>
       </c>
       <c r="D54" t="n">
-        <v>863.51</v>
+        <v>446.85</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>113214.37</v>
+        <v>113118.66</v>
       </c>
       <c r="C55" t="n">
-        <v>119055.9</v>
+        <v>114512.77</v>
       </c>
       <c r="D55" t="n">
-        <v>5841.53</v>
+        <v>1394.11</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>110807.88</v>
+        <v>110783.16</v>
       </c>
       <c r="C56" t="n">
-        <v>112359.59</v>
+        <v>112804.22</v>
       </c>
       <c r="D56" t="n">
-        <v>1551.71</v>
+        <v>2021.06</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>115169.77</v>
+        <v>108186.04</v>
       </c>
       <c r="C57" t="n">
-        <v>112704.22</v>
+        <v>111139.74</v>
       </c>
       <c r="D57" t="n">
-        <v>-2465.55</v>
+        <v>2953.7</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>115271.08</v>
+        <v>106467.79</v>
       </c>
       <c r="C58" t="n">
-        <v>115833.15</v>
+        <v>107863.17</v>
       </c>
       <c r="D58" t="n">
-        <v>562.0700000000001</v>
+        <v>1395.39</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>113118.66</v>
+        <v>107198.27</v>
       </c>
       <c r="C59" t="n">
-        <v>114555.47</v>
+        <v>106337.68</v>
       </c>
       <c r="D59" t="n">
-        <v>1436.8</v>
+        <v>-860.58</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>110783.16</v>
+        <v>108666.71</v>
       </c>
       <c r="C60" t="n">
-        <v>112874.19</v>
+        <v>107764.3</v>
       </c>
       <c r="D60" t="n">
-        <v>2091.02</v>
+        <v>-902.41</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>108186.04</v>
+        <v>110588.93</v>
       </c>
       <c r="C61" t="n">
-        <v>111223.64</v>
+        <v>109648.02</v>
       </c>
       <c r="D61" t="n">
-        <v>3037.6</v>
+        <v>-940.91</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>106467.79</v>
+        <v>108476.89</v>
       </c>
       <c r="C62" t="n">
-        <v>107918.51</v>
+        <v>110055.34</v>
       </c>
       <c r="D62" t="n">
-        <v>1450.72</v>
+        <v>1578.45</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>107198.27</v>
+        <v>107688.59</v>
       </c>
       <c r="C63" t="n">
-        <v>106397.3</v>
+        <v>108530.46</v>
       </c>
       <c r="D63" t="n">
-        <v>-800.97</v>
+        <v>841.87</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>108666.71</v>
+        <v>110069.73</v>
       </c>
       <c r="C64" t="n">
-        <v>107851.52</v>
+        <v>108647.57</v>
       </c>
       <c r="D64" t="n">
-        <v>-815.2</v>
+        <v>-1422.16</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>110588.93</v>
+        <v>111033.92</v>
       </c>
       <c r="C65" t="n">
-        <v>109723.63</v>
+        <v>110232.14</v>
       </c>
       <c r="D65" t="n">
-        <v>-865.3</v>
+        <v>-801.79</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-25</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>108476.89</v>
+        <v>111641.73</v>
       </c>
       <c r="C66" t="n">
-        <v>110112.24</v>
+        <v>110805.43</v>
       </c>
       <c r="D66" t="n">
-        <v>1635.35</v>
+        <v>-836.29</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>107688.59</v>
+        <v>114472.45</v>
       </c>
       <c r="C67" t="n">
-        <v>108549.15</v>
+        <v>112303.66</v>
       </c>
       <c r="D67" t="n">
-        <v>860.5599999999999</v>
+        <v>-2168.79</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>110069.73</v>
+        <v>114119.33</v>
       </c>
       <c r="C68" t="n">
-        <v>108685.72</v>
+        <v>114436.45</v>
       </c>
       <c r="D68" t="n">
-        <v>-1384.01</v>
+        <v>317.13</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>111033.92</v>
+        <v>112956.16</v>
       </c>
       <c r="C69" t="n">
-        <v>110265.73</v>
+        <v>113677.87</v>
       </c>
       <c r="D69" t="n">
-        <v>-768.1900000000001</v>
+        <v>721.7</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2025-10-25</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>111641.73</v>
+        <v>110055.3</v>
       </c>
       <c r="C70" t="n">
-        <v>110803.23</v>
+        <v>111489.76</v>
       </c>
       <c r="D70" t="n">
-        <v>-838.5</v>
+        <v>1434.46</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>114472.45</v>
+        <v>108305.55</v>
       </c>
       <c r="C71" t="n">
-        <v>112317.65</v>
+        <v>109319.44</v>
       </c>
       <c r="D71" t="n">
-        <v>-2154.8</v>
+        <v>1013.9</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>114119.33</v>
+        <v>109556.16</v>
       </c>
       <c r="C72" t="n">
-        <v>114458.86</v>
+        <v>108581.49</v>
       </c>
       <c r="D72" t="n">
-        <v>339.54</v>
+        <v>-974.67</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>112956.16</v>
+        <v>110064.02</v>
       </c>
       <c r="C73" t="n">
-        <v>113663.47</v>
+        <v>109322.63</v>
       </c>
       <c r="D73" t="n">
-        <v>707.3</v>
+        <v>-741.38</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>110055.3</v>
+        <v>110639.62</v>
       </c>
       <c r="C74" t="n">
-        <v>111493.3</v>
+        <v>110129.59</v>
       </c>
       <c r="D74" t="n">
-        <v>1437.99</v>
+        <v>-510.03</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>108305.55</v>
+        <v>106547.52</v>
       </c>
       <c r="C75" t="n">
-        <v>109337.25</v>
+        <v>109107.13</v>
       </c>
       <c r="D75" t="n">
-        <v>1031.7</v>
+        <v>2559.6</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>109556.16</v>
+        <v>101590.52</v>
       </c>
       <c r="C76" t="n">
-        <v>108639.78</v>
+        <v>104940.03</v>
       </c>
       <c r="D76" t="n">
-        <v>-916.38</v>
+        <v>3349.51</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>110064.02</v>
+        <v>103891.84</v>
       </c>
       <c r="C77" t="n">
-        <v>109393.62</v>
+        <v>102475.35</v>
       </c>
       <c r="D77" t="n">
-        <v>-670.4</v>
+        <v>-1416.49</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>110639.62</v>
+        <v>101301.29</v>
       </c>
       <c r="C78" t="n">
-        <v>110197.91</v>
+        <v>102482.89</v>
       </c>
       <c r="D78" t="n">
-        <v>-441.71</v>
+        <v>1181.6</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>106547.52</v>
+        <v>103372.41</v>
       </c>
       <c r="C79" t="n">
-        <v>109179.94</v>
+        <v>101919.71</v>
       </c>
       <c r="D79" t="n">
-        <v>2632.42</v>
+        <v>-1452.7</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>101590.52</v>
+        <v>102282.12</v>
       </c>
       <c r="C80" t="n">
-        <v>104995.49</v>
+        <v>102483.95</v>
       </c>
       <c r="D80" t="n">
-        <v>3404.96</v>
+        <v>201.83</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>103891.84</v>
+        <v>104719.64</v>
       </c>
       <c r="C81" t="n">
-        <v>102560.24</v>
+        <v>103771.11</v>
       </c>
       <c r="D81" t="n">
-        <v>-1331.6</v>
+        <v>-948.53</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>101301.29</v>
+        <v>105996.59</v>
       </c>
       <c r="C82" t="n">
-        <v>102591.89</v>
+        <v>105294.18</v>
       </c>
       <c r="D82" t="n">
-        <v>1290.6</v>
+        <v>-702.42</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>103372.41</v>
+        <v>102997.47</v>
       </c>
       <c r="C83" t="n">
-        <v>101987.12</v>
+        <v>104669.44</v>
       </c>
       <c r="D83" t="n">
-        <v>-1385.28</v>
+        <v>1671.97</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>102282.12</v>
+        <v>101663.19</v>
       </c>
       <c r="C84" t="n">
-        <v>102598.25</v>
+        <v>102342.28</v>
       </c>
       <c r="D84" t="n">
-        <v>316.14</v>
+        <v>679.1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>104719.64</v>
+        <v>99697.49000000001</v>
       </c>
       <c r="C85" t="n">
-        <v>103829.4</v>
+        <v>100534.46</v>
       </c>
       <c r="D85" t="n">
-        <v>-890.25</v>
+        <v>836.97</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>105996.59</v>
+        <v>94397.78999999999</v>
       </c>
       <c r="C86" t="n">
-        <v>105362.05</v>
+        <v>97468.25</v>
       </c>
       <c r="D86" t="n">
-        <v>-634.55</v>
+        <v>3070.46</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>102997.47</v>
+        <v>95549.14999999999</v>
       </c>
       <c r="C87" t="n">
-        <v>104690.55</v>
+        <v>94513.10000000001</v>
       </c>
       <c r="D87" t="n">
-        <v>1693.08</v>
+        <v>-1036.05</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>101663.19</v>
+        <v>94177.08</v>
       </c>
       <c r="C88" t="n">
-        <v>102365.3</v>
+        <v>94840.27</v>
       </c>
       <c r="D88" t="n">
-        <v>702.11</v>
+        <v>663.1900000000001</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>99697.49000000001</v>
+        <v>92093.88</v>
       </c>
       <c r="C89" t="n">
-        <v>100581.55</v>
+        <v>93811.89</v>
       </c>
       <c r="D89" t="n">
-        <v>884.05</v>
+        <v>1718.01</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>94397.78999999999</v>
+        <v>92948.88</v>
       </c>
       <c r="C90" t="n">
-        <v>97513.74000000001</v>
+        <v>92561.52</v>
       </c>
       <c r="D90" t="n">
-        <v>3115.95</v>
+        <v>-387.35</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>95549.14999999999</v>
+        <v>91465.99000000001</v>
       </c>
       <c r="C91" t="n">
-        <v>94557.39</v>
+        <v>92733.00999999999</v>
       </c>
       <c r="D91" t="n">
-        <v>-991.76</v>
+        <v>1267.02</v>
       </c>
     </row>
   </sheetData>

--- a/exports/btc-usd_predictions_last90.xlsx
+++ b/exports/btc-usd_predictions_last90.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D91"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,1446 +449,2669 @@
           <t>diff</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>diff_pct</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>train_start_date</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>train_end_date</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>116874.09</v>
+        <v>113458.43</v>
       </c>
       <c r="C2" t="n">
-        <v>114018.56</v>
+        <v>116245.83</v>
       </c>
       <c r="D2" t="n">
-        <v>-2855.52</v>
+        <v>2787.4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>115374.33</v>
+        <v>110124.35</v>
       </c>
       <c r="C3" t="n">
-        <v>116015.67</v>
+        <v>115340.69</v>
       </c>
       <c r="D3" t="n">
-        <v>641.34</v>
+        <v>5216.34</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>113458.43</v>
+        <v>111802.66</v>
       </c>
       <c r="C4" t="n">
-        <v>115040.63</v>
+        <v>112614.99</v>
       </c>
       <c r="D4" t="n">
-        <v>1582.2</v>
+        <v>812.33</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>110124.35</v>
+        <v>111222.06</v>
       </c>
       <c r="C5" t="n">
-        <v>112355.35</v>
+        <v>110947.93</v>
       </c>
       <c r="D5" t="n">
-        <v>2231</v>
+        <v>-274.13</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>111802.66</v>
+        <v>112544.8</v>
       </c>
       <c r="C6" t="n">
-        <v>110806.5</v>
+        <v>111581.89</v>
       </c>
       <c r="D6" t="n">
-        <v>-996.16</v>
+        <v>-962.91</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>111222.06</v>
+        <v>108410.84</v>
       </c>
       <c r="C7" t="n">
-        <v>111414.71</v>
+        <v>111450.69</v>
       </c>
       <c r="D7" t="n">
-        <v>192.65</v>
+        <v>3039.86</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>112544.8</v>
+        <v>108808.07</v>
       </c>
       <c r="C8" t="n">
-        <v>111297.07</v>
+        <v>111292.26</v>
       </c>
       <c r="D8" t="n">
-        <v>-1247.74</v>
+        <v>2484.19</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>108410.84</v>
+        <v>108236.71</v>
       </c>
       <c r="C9" t="n">
-        <v>111002.02</v>
+        <v>109193.57</v>
       </c>
       <c r="D9" t="n">
-        <v>2591.18</v>
+        <v>956.85</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>108808.07</v>
+        <v>109250.59</v>
       </c>
       <c r="C10" t="n">
-        <v>109038.09</v>
+        <v>108953.16</v>
       </c>
       <c r="D10" t="n">
-        <v>230.02</v>
+        <v>-297.44</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>108236.71</v>
+        <v>111200.59</v>
       </c>
       <c r="C11" t="n">
-        <v>108772.81</v>
+        <v>108790.64</v>
       </c>
       <c r="D11" t="n">
-        <v>536.1</v>
+        <v>-2409.95</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-2.17</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>109250.59</v>
+        <v>111723.21</v>
       </c>
       <c r="C12" t="n">
-        <v>108667.43</v>
+        <v>109910.75</v>
       </c>
       <c r="D12" t="n">
-        <v>-583.16</v>
+        <v>-1812.46</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-1.62</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>111200.59</v>
+        <v>110723.6</v>
       </c>
       <c r="C13" t="n">
-        <v>109760.84</v>
+        <v>111390.89</v>
       </c>
       <c r="D13" t="n">
-        <v>-1439.75</v>
+        <v>667.29</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>111723.21</v>
+        <v>110650.98</v>
       </c>
       <c r="C14" t="n">
-        <v>111285.79</v>
+        <v>111699.25</v>
       </c>
       <c r="D14" t="n">
-        <v>-437.42</v>
+        <v>1048.27</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>110723.6</v>
+        <v>110224.7</v>
       </c>
       <c r="C15" t="n">
-        <v>111589.03</v>
+        <v>110654.3</v>
       </c>
       <c r="D15" t="n">
-        <v>865.4299999999999</v>
+        <v>429.6</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>110650.98</v>
+        <v>111167.62</v>
       </c>
       <c r="C16" t="n">
-        <v>110572.61</v>
+        <v>110379.78</v>
       </c>
       <c r="D16" t="n">
-        <v>-78.37</v>
+        <v>-787.84</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>110224.7</v>
+        <v>112071.43</v>
       </c>
       <c r="C17" t="n">
-        <v>110346.66</v>
+        <v>110291</v>
       </c>
       <c r="D17" t="n">
-        <v>121.97</v>
+        <v>-1780.43</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-1.59</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2025-09-07</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>111167.62</v>
+        <v>111530.55</v>
       </c>
       <c r="C18" t="n">
-        <v>110210.01</v>
+        <v>111143.53</v>
       </c>
       <c r="D18" t="n">
-        <v>-957.6</v>
+        <v>-387.02</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>112071.43</v>
+        <v>113955.36</v>
       </c>
       <c r="C19" t="n">
-        <v>110988.82</v>
+        <v>111780.77</v>
       </c>
       <c r="D19" t="n">
-        <v>-1082.61</v>
+        <v>-2174.59</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-1.91</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>111530.55</v>
+        <v>115507.54</v>
       </c>
       <c r="C20" t="n">
-        <v>111630.29</v>
+        <v>112336.23</v>
       </c>
       <c r="D20" t="n">
-        <v>99.75</v>
+        <v>-3171.31</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>113955.36</v>
+        <v>116101.58</v>
       </c>
       <c r="C21" t="n">
-        <v>112184.35</v>
+        <v>114236.73</v>
       </c>
       <c r="D21" t="n">
-        <v>-1771.01</v>
+        <v>-1864.85</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-1.61</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>115507.54</v>
+        <v>115950.51</v>
       </c>
       <c r="C22" t="n">
-        <v>114106.48</v>
+        <v>115485.73</v>
       </c>
       <c r="D22" t="n">
-        <v>-1401.05</v>
+        <v>-464.78</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>116101.58</v>
+        <v>115407.66</v>
       </c>
       <c r="C23" t="n">
-        <v>115315.55</v>
+        <v>115398.82</v>
       </c>
       <c r="D23" t="n">
-        <v>-786.03</v>
+        <v>-8.83</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>115950.51</v>
+        <v>115444.88</v>
       </c>
       <c r="C24" t="n">
-        <v>115335.68</v>
+        <v>115454.65</v>
       </c>
       <c r="D24" t="n">
-        <v>-614.83</v>
+        <v>9.77</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>115407.66</v>
+        <v>116843.19</v>
       </c>
       <c r="C25" t="n">
-        <v>115352.46</v>
+        <v>115308.36</v>
       </c>
       <c r="D25" t="n">
-        <v>-55.19</v>
+        <v>-1534.82</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-1.31</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>115444.88</v>
+        <v>116468.51</v>
       </c>
       <c r="C26" t="n">
-        <v>115123.87</v>
+        <v>115467.86</v>
       </c>
       <c r="D26" t="n">
-        <v>-321</v>
+        <v>-1000.65</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>116843.19</v>
+        <v>117137.2</v>
       </c>
       <c r="C27" t="n">
-        <v>115348.47</v>
+        <v>116417.84</v>
       </c>
       <c r="D27" t="n">
-        <v>-1494.72</v>
+        <v>-719.36</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>116468.51</v>
+        <v>115688.86</v>
       </c>
       <c r="C28" t="n">
-        <v>116236.09</v>
+        <v>116546.15</v>
       </c>
       <c r="D28" t="n">
-        <v>-232.42</v>
+        <v>857.29</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>117137.2</v>
+        <v>115721.96</v>
       </c>
       <c r="C29" t="n">
-        <v>116439.63</v>
+        <v>116682.63</v>
       </c>
       <c r="D29" t="n">
-        <v>-697.58</v>
+        <v>960.67</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>115688.86</v>
+        <v>115306.09</v>
       </c>
       <c r="C30" t="n">
-        <v>116514.53</v>
+        <v>115829.8</v>
       </c>
       <c r="D30" t="n">
-        <v>825.67</v>
+        <v>523.71</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>115721.96</v>
+        <v>112748.51</v>
       </c>
       <c r="C31" t="n">
-        <v>115734.45</v>
+        <v>115621.82</v>
       </c>
       <c r="D31" t="n">
-        <v>12.48</v>
+        <v>2873.31</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>115306.09</v>
+        <v>112014.5</v>
       </c>
       <c r="C32" t="n">
-        <v>115400.58</v>
+        <v>114634.09</v>
       </c>
       <c r="D32" t="n">
-        <v>94.48999999999999</v>
+        <v>2619.59</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>112748.51</v>
+        <v>113328.63</v>
       </c>
       <c r="C33" t="n">
-        <v>114235.36</v>
+        <v>112595.38</v>
       </c>
       <c r="D33" t="n">
-        <v>1486.85</v>
+        <v>-733.25</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>112014.5</v>
+        <v>109049.29</v>
       </c>
       <c r="C34" t="n">
-        <v>112434.18</v>
+        <v>112637.24</v>
       </c>
       <c r="D34" t="n">
-        <v>419.68</v>
+        <v>3587.95</v>
+      </c>
+      <c r="E34" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>113328.63</v>
+        <v>109712.83</v>
       </c>
       <c r="C35" t="n">
-        <v>112460.82</v>
+        <v>112316.21</v>
       </c>
       <c r="D35" t="n">
-        <v>-867.8099999999999</v>
+        <v>2603.38</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>109049.29</v>
+        <v>109681.95</v>
       </c>
       <c r="C36" t="n">
-        <v>112045.83</v>
+        <v>109601.7</v>
       </c>
       <c r="D36" t="n">
-        <v>2996.54</v>
+        <v>-80.23999999999999</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>109712.83</v>
+        <v>112122.64</v>
       </c>
       <c r="C37" t="n">
-        <v>109441.45</v>
+        <v>109930.78</v>
       </c>
       <c r="D37" t="n">
-        <v>-271.38</v>
+        <v>-2191.86</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-1.95</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>109681.95</v>
+        <v>114400.38</v>
       </c>
       <c r="C38" t="n">
-        <v>109761.02</v>
+        <v>111145.9</v>
       </c>
       <c r="D38" t="n">
-        <v>79.06999999999999</v>
+        <v>-3254.49</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-2.84</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>112122.64</v>
+        <v>114056.09</v>
       </c>
       <c r="C39" t="n">
-        <v>111010.85</v>
+        <v>112964.26</v>
       </c>
       <c r="D39" t="n">
-        <v>-1111.79</v>
+        <v>-1091.83</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>114400.38</v>
+        <v>118648.93</v>
       </c>
       <c r="C40" t="n">
-        <v>112761.19</v>
+        <v>114288.99</v>
       </c>
       <c r="D40" t="n">
-        <v>-1639.2</v>
+        <v>-4359.94</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-3.67</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>114056.09</v>
+        <v>120681.26</v>
       </c>
       <c r="C41" t="n">
-        <v>114198.43</v>
+        <v>115907</v>
       </c>
       <c r="D41" t="n">
-        <v>142.34</v>
+        <v>-4774.26</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-3.96</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>118648.93</v>
+        <v>122266.53</v>
       </c>
       <c r="C42" t="n">
-        <v>115801.38</v>
+        <v>118880.58</v>
       </c>
       <c r="D42" t="n">
-        <v>-2847.55</v>
+        <v>-3385.95</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-2.77</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>120681.26</v>
+        <v>122425.43</v>
       </c>
       <c r="C43" t="n">
-        <v>118819.74</v>
+        <v>120781.4</v>
       </c>
       <c r="D43" t="n">
-        <v>-1861.51</v>
+        <v>-1644.03</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-1.34</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>122266.53</v>
+        <v>123513.48</v>
       </c>
       <c r="C44" t="n">
-        <v>120716.81</v>
+        <v>121376.4</v>
       </c>
       <c r="D44" t="n">
-        <v>-1549.72</v>
+        <v>-2137.08</v>
+      </c>
+      <c r="E44" t="n">
+        <v>-1.73</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2025-10-04</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>122425.43</v>
+        <v>124752.53</v>
       </c>
       <c r="C45" t="n">
-        <v>121380.3</v>
+        <v>122373.81</v>
       </c>
       <c r="D45" t="n">
-        <v>-1045.12</v>
+        <v>-2378.73</v>
+      </c>
+      <c r="E45" t="n">
+        <v>-1.91</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>123513.48</v>
+        <v>121451.38</v>
       </c>
       <c r="C46" t="n">
-        <v>122271.32</v>
+        <v>123502.26</v>
       </c>
       <c r="D46" t="n">
-        <v>-1242.15</v>
+        <v>2050.88</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>124752.53</v>
+        <v>123354.87</v>
       </c>
       <c r="C47" t="n">
-        <v>123443.39</v>
+        <v>123102.93</v>
       </c>
       <c r="D47" t="n">
-        <v>-1309.14</v>
+        <v>-251.94</v>
+      </c>
+      <c r="E47" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>121451.38</v>
+        <v>121705.59</v>
       </c>
       <c r="C48" t="n">
-        <v>123009.88</v>
+        <v>121811.82</v>
       </c>
       <c r="D48" t="n">
-        <v>1558.49</v>
+        <v>106.24</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>123354.87</v>
+        <v>113214.37</v>
       </c>
       <c r="C49" t="n">
-        <v>121759.14</v>
+        <v>122673.01</v>
       </c>
       <c r="D49" t="n">
-        <v>-1595.73</v>
+        <v>9458.639999999999</v>
+      </c>
+      <c r="E49" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>121705.59</v>
+        <v>110807.88</v>
       </c>
       <c r="C50" t="n">
-        <v>122529.17</v>
+        <v>119371.69</v>
       </c>
       <c r="D50" t="n">
-        <v>823.58</v>
+        <v>8563.809999999999</v>
+      </c>
+      <c r="E50" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>113214.37</v>
+        <v>115169.77</v>
       </c>
       <c r="C51" t="n">
-        <v>119047.49</v>
+        <v>112400.83</v>
       </c>
       <c r="D51" t="n">
-        <v>5833.12</v>
+        <v>-2768.94</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2025-10-11</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>110807.88</v>
+        <v>115271.08</v>
       </c>
       <c r="C52" t="n">
-        <v>112331.47</v>
+        <v>112694.67</v>
       </c>
       <c r="D52" t="n">
-        <v>1523.59</v>
+        <v>-2576.41</v>
+      </c>
+      <c r="E52" t="n">
+        <v>-2.24</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>115169.77</v>
+        <v>113118.66</v>
       </c>
       <c r="C53" t="n">
-        <v>112581.73</v>
+        <v>116008.87</v>
       </c>
       <c r="D53" t="n">
-        <v>-2588.03</v>
+        <v>2890.21</v>
+      </c>
+      <c r="E53" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>115271.08</v>
+        <v>110783.16</v>
       </c>
       <c r="C54" t="n">
-        <v>115717.93</v>
+        <v>114865.92</v>
       </c>
       <c r="D54" t="n">
-        <v>446.85</v>
+        <v>4082.76</v>
+      </c>
+      <c r="E54" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>113118.66</v>
+        <v>108186.04</v>
       </c>
       <c r="C55" t="n">
-        <v>114512.77</v>
+        <v>113083.91</v>
       </c>
       <c r="D55" t="n">
-        <v>1394.11</v>
+        <v>4897.87</v>
+      </c>
+      <c r="E55" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>110783.16</v>
+        <v>106467.79</v>
       </c>
       <c r="C56" t="n">
-        <v>112804.22</v>
+        <v>111370.74</v>
       </c>
       <c r="D56" t="n">
-        <v>2021.06</v>
+        <v>4902.95</v>
+      </c>
+      <c r="E56" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>108186.04</v>
+        <v>107198.27</v>
       </c>
       <c r="C57" t="n">
-        <v>111139.74</v>
+        <v>108026.67</v>
       </c>
       <c r="D57" t="n">
-        <v>2953.7</v>
+        <v>828.41</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>106467.79</v>
+        <v>108666.71</v>
       </c>
       <c r="C58" t="n">
-        <v>107863.17</v>
+        <v>106444.55</v>
       </c>
       <c r="D58" t="n">
-        <v>1395.39</v>
+        <v>-2222.16</v>
+      </c>
+      <c r="E58" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>107198.27</v>
+        <v>110588.93</v>
       </c>
       <c r="C59" t="n">
-        <v>106337.68</v>
+        <v>107913.9</v>
       </c>
       <c r="D59" t="n">
-        <v>-860.58</v>
+        <v>-2675.03</v>
+      </c>
+      <c r="E59" t="n">
+        <v>-2.42</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>108666.71</v>
+        <v>108476.89</v>
       </c>
       <c r="C60" t="n">
-        <v>107764.3</v>
+        <v>109833.73</v>
       </c>
       <c r="D60" t="n">
-        <v>-902.41</v>
+        <v>1356.84</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>110588.93</v>
+        <v>107688.59</v>
       </c>
       <c r="C61" t="n">
-        <v>109648.02</v>
+        <v>110239.45</v>
       </c>
       <c r="D61" t="n">
-        <v>-940.91</v>
+        <v>2550.87</v>
+      </c>
+      <c r="E61" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>108476.89</v>
+        <v>110069.73</v>
       </c>
       <c r="C62" t="n">
-        <v>110055.34</v>
+        <v>108626.5</v>
       </c>
       <c r="D62" t="n">
-        <v>1578.45</v>
+        <v>-1443.23</v>
+      </c>
+      <c r="E62" t="n">
+        <v>-1.31</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>107688.59</v>
+        <v>111033.92</v>
       </c>
       <c r="C63" t="n">
-        <v>108530.46</v>
+        <v>108742.77</v>
       </c>
       <c r="D63" t="n">
-        <v>841.87</v>
+        <v>-2291.15</v>
+      </c>
+      <c r="E63" t="n">
+        <v>-2.06</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-25</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>110069.73</v>
+        <v>111641.73</v>
       </c>
       <c r="C64" t="n">
-        <v>108647.57</v>
+        <v>110328.07</v>
       </c>
       <c r="D64" t="n">
-        <v>-1422.16</v>
+        <v>-1313.65</v>
+      </c>
+      <c r="E64" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>111033.92</v>
+        <v>114472.45</v>
       </c>
       <c r="C65" t="n">
-        <v>110232.14</v>
+        <v>110835.86</v>
       </c>
       <c r="D65" t="n">
-        <v>-801.79</v>
+        <v>-3636.59</v>
+      </c>
+      <c r="E65" t="n">
+        <v>-3.18</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2025-10-25</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>111641.73</v>
+        <v>114119.33</v>
       </c>
       <c r="C66" t="n">
-        <v>110805.43</v>
+        <v>112419.55</v>
       </c>
       <c r="D66" t="n">
-        <v>-836.29</v>
+        <v>-1699.78</v>
+      </c>
+      <c r="E66" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>114472.45</v>
+        <v>112956.16</v>
       </c>
       <c r="C67" t="n">
-        <v>112303.66</v>
+        <v>114538.1</v>
       </c>
       <c r="D67" t="n">
-        <v>-2168.79</v>
+        <v>1581.93</v>
+      </c>
+      <c r="E67" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>114119.33</v>
+        <v>110055.3</v>
       </c>
       <c r="C68" t="n">
-        <v>114436.45</v>
+        <v>113789.45</v>
       </c>
       <c r="D68" t="n">
-        <v>317.13</v>
+        <v>3734.14</v>
+      </c>
+      <c r="E68" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>112956.16</v>
+        <v>108305.55</v>
       </c>
       <c r="C69" t="n">
-        <v>113677.87</v>
+        <v>111620.97</v>
       </c>
       <c r="D69" t="n">
-        <v>721.7</v>
+        <v>3315.42</v>
+      </c>
+      <c r="E69" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>110055.3</v>
+        <v>109556.16</v>
       </c>
       <c r="C70" t="n">
-        <v>111489.76</v>
+        <v>109437.32</v>
       </c>
       <c r="D70" t="n">
-        <v>1434.46</v>
+        <v>-118.84</v>
+      </c>
+      <c r="E70" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>108305.55</v>
+        <v>110064.02</v>
       </c>
       <c r="C71" t="n">
-        <v>109319.44</v>
+        <v>108751.54</v>
       </c>
       <c r="D71" t="n">
-        <v>1013.9</v>
+        <v>-1312.47</v>
+      </c>
+      <c r="E71" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>109556.16</v>
+        <v>110639.62</v>
       </c>
       <c r="C72" t="n">
-        <v>108581.49</v>
+        <v>109495.21</v>
       </c>
       <c r="D72" t="n">
-        <v>-974.67</v>
+        <v>-1144.42</v>
+      </c>
+      <c r="E72" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>110064.02</v>
+        <v>106547.52</v>
       </c>
       <c r="C73" t="n">
-        <v>109322.63</v>
+        <v>110348.15</v>
       </c>
       <c r="D73" t="n">
-        <v>-741.38</v>
+        <v>3800.62</v>
+      </c>
+      <c r="E73" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>110639.62</v>
+        <v>101590.52</v>
       </c>
       <c r="C74" t="n">
-        <v>110129.59</v>
+        <v>109339.14</v>
       </c>
       <c r="D74" t="n">
-        <v>-510.03</v>
+        <v>7748.62</v>
+      </c>
+      <c r="E74" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>106547.52</v>
+        <v>103891.84</v>
       </c>
       <c r="C75" t="n">
-        <v>109107.13</v>
+        <v>105110.55</v>
       </c>
       <c r="D75" t="n">
-        <v>2559.6</v>
+        <v>1218.71</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>101590.52</v>
+        <v>101301.29</v>
       </c>
       <c r="C76" t="n">
-        <v>104940.03</v>
+        <v>102697.09</v>
       </c>
       <c r="D76" t="n">
-        <v>3349.51</v>
+        <v>1395.8</v>
+      </c>
+      <c r="E76" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>103891.84</v>
+        <v>103372.41</v>
       </c>
       <c r="C77" t="n">
-        <v>102475.35</v>
+        <v>102650.56</v>
       </c>
       <c r="D77" t="n">
-        <v>-1416.49</v>
+        <v>-721.85</v>
+      </c>
+      <c r="E77" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>101301.29</v>
+        <v>102282.12</v>
       </c>
       <c r="C78" t="n">
-        <v>102482.89</v>
+        <v>102021.38</v>
       </c>
       <c r="D78" t="n">
-        <v>1181.6</v>
+        <v>-260.74</v>
+      </c>
+      <c r="E78" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>103372.41</v>
+        <v>104719.64</v>
       </c>
       <c r="C79" t="n">
-        <v>101919.71</v>
+        <v>102631.1</v>
       </c>
       <c r="D79" t="n">
-        <v>-1452.7</v>
+        <v>-2088.54</v>
+      </c>
+      <c r="E79" t="n">
+        <v>-1.99</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>102282.12</v>
+        <v>105996.59</v>
       </c>
       <c r="C80" t="n">
-        <v>102483.95</v>
+        <v>103841.03</v>
       </c>
       <c r="D80" t="n">
-        <v>201.83</v>
+        <v>-2155.56</v>
+      </c>
+      <c r="E80" t="n">
+        <v>-2.03</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>104719.64</v>
+        <v>102997.47</v>
       </c>
       <c r="C81" t="n">
-        <v>103771.11</v>
+        <v>105419.25</v>
       </c>
       <c r="D81" t="n">
-        <v>-948.53</v>
+        <v>2421.78</v>
+      </c>
+      <c r="E81" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>105996.59</v>
+        <v>101663.19</v>
       </c>
       <c r="C82" t="n">
-        <v>105294.18</v>
+        <v>104754.03</v>
       </c>
       <c r="D82" t="n">
-        <v>-702.42</v>
+        <v>3090.84</v>
+      </c>
+      <c r="E82" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>102997.47</v>
+        <v>99697.49000000001</v>
       </c>
       <c r="C83" t="n">
-        <v>104669.44</v>
+        <v>102436.31</v>
       </c>
       <c r="D83" t="n">
-        <v>1671.97</v>
+        <v>2738.82</v>
+      </c>
+      <c r="E83" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>101663.19</v>
+        <v>94397.78999999999</v>
       </c>
       <c r="C84" t="n">
-        <v>102342.28</v>
+        <v>100672.29</v>
       </c>
       <c r="D84" t="n">
-        <v>679.1</v>
+        <v>6274.5</v>
+      </c>
+      <c r="E84" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>99697.49000000001</v>
+        <v>95549.14999999999</v>
       </c>
       <c r="C85" t="n">
-        <v>100534.46</v>
+        <v>97531.95</v>
       </c>
       <c r="D85" t="n">
-        <v>836.97</v>
+        <v>1982.81</v>
+      </c>
+      <c r="E85" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>94397.78999999999</v>
+        <v>94177.08</v>
       </c>
       <c r="C86" t="n">
-        <v>97468.25</v>
+        <v>94563.33</v>
       </c>
       <c r="D86" t="n">
-        <v>3070.46</v>
+        <v>386.25</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>95549.14999999999</v>
+        <v>92093.88</v>
       </c>
       <c r="C87" t="n">
-        <v>94513.10000000001</v>
+        <v>94950.14999999999</v>
       </c>
       <c r="D87" t="n">
-        <v>-1036.05</v>
+        <v>2856.28</v>
+      </c>
+      <c r="E87" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>94177.08</v>
+        <v>92948.88</v>
       </c>
       <c r="C88" t="n">
-        <v>94840.27</v>
+        <v>93876.50999999999</v>
       </c>
       <c r="D88" t="n">
-        <v>663.1900000000001</v>
+        <v>927.64</v>
+      </c>
+      <c r="E88" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>92093.88</v>
+        <v>91465.99000000001</v>
       </c>
       <c r="C89" t="n">
-        <v>93811.89</v>
+        <v>92624.73</v>
       </c>
       <c r="D89" t="n">
-        <v>1718.01</v>
+        <v>1158.74</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>92948.88</v>
+        <v>86631.89999999999</v>
       </c>
       <c r="C90" t="n">
-        <v>92561.52</v>
+        <v>92792.94</v>
       </c>
       <c r="D90" t="n">
-        <v>-387.35</v>
+        <v>6161.05</v>
+      </c>
+      <c r="E90" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>91465.99000000001</v>
+        <v>85090.69</v>
       </c>
       <c r="C91" t="n">
-        <v>92733.00999999999</v>
+        <v>89784.86</v>
       </c>
       <c r="D91" t="n">
-        <v>1267.02</v>
-      </c>
+        <v>4694.17</v>
+      </c>
+      <c r="E91" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2020-06-01</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>AVG</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="n">
+        <v>603.23</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>AVG_TRIM</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>(ex max/min)</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="n">
+        <v>563.71</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
